--- a/CSV/Nether Fortress.xlsx
+++ b/CSV/Nether Fortress.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\friend-zone\XLSX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willem/Documents/GitHub/friend-zone/CSV/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{177A4053-8EEE-47CC-8C7F-813239FCD8CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0516CCA3-D947-B342-9048-5C8F96BB290B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{EF5563DD-86E3-44AF-B99F-9E11ACF57133}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" xr2:uid="{EF5563DD-86E3-44AF-B99F-9E11ACF57133}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,29 +34,20 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="5">
-  <si>
-    <t>nummer</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Z</t>
-  </si>
-  <si>
-    <t>/tp</t>
   </si>
   <si>
     <t>x</t>
   </si>
   <si>
-    <t>Y</t>
+    <t>Nether Fortress</t>
   </si>
 </sst>
 </file>
@@ -441,113 +432,372 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2061EA4-28D3-4349-9580-4EA67BE3ACE4}">
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>2</v>
+      <c r="B2">
+        <v>2283</v>
       </c>
       <c r="C2">
-        <v>-3347</v>
-      </c>
-      <c r="D2">
-        <v>71</v>
-      </c>
-      <c r="E2">
-        <v>-2979</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-949</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>2</v>
+      <c r="B3">
+        <v>2171</v>
       </c>
       <c r="C3">
-        <v>-3246</v>
-      </c>
-      <c r="D3">
-        <v>112</v>
-      </c>
-      <c r="E3">
-        <v>-2606</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-1381</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>2</v>
+      <c r="B4">
+        <v>2123</v>
       </c>
       <c r="C4">
-        <v>-3476</v>
-      </c>
-      <c r="D4">
-        <v>102</v>
-      </c>
-      <c r="E4">
-        <v>-1589</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>2</v>
+      <c r="B5">
+        <v>1771</v>
       </c>
       <c r="C5">
-        <v>793</v>
-      </c>
-      <c r="D5">
-        <v>82</v>
-      </c>
-      <c r="E5">
-        <v>2915</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>2</v>
+      <c r="B6">
+        <v>1083</v>
       </c>
       <c r="C6">
-        <v>776</v>
-      </c>
-      <c r="D6">
-        <v>84</v>
-      </c>
-      <c r="E6">
-        <v>2906</v>
+        <v>-165</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1051</v>
+      </c>
+      <c r="C7">
+        <v>-1045</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1051</v>
+      </c>
+      <c r="C8">
+        <v>-2277</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>891</v>
+      </c>
+      <c r="C9">
+        <v>-2069</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>523</v>
+      </c>
+      <c r="C10">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>283</v>
+      </c>
+      <c r="C11">
+        <v>-757</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>219</v>
+      </c>
+      <c r="C12">
+        <v>-1045</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>171</v>
+      </c>
+      <c r="C13">
+        <v>-357</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>139</v>
+      </c>
+      <c r="C14">
+        <v>-2037</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>-69</v>
+      </c>
+      <c r="C15">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>-101</v>
+      </c>
+      <c r="C16">
+        <v>-1829</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>-245</v>
+      </c>
+      <c r="C17">
+        <v>-661</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>-277</v>
+      </c>
+      <c r="C18">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>-629</v>
+      </c>
+      <c r="C19">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>-693</v>
+      </c>
+      <c r="C20">
+        <v>-1541</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>-693</v>
+      </c>
+      <c r="C21">
+        <v>-789</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>-869</v>
+      </c>
+      <c r="C22">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>-1061</v>
+      </c>
+      <c r="C23">
+        <v>-1989</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>-1061</v>
+      </c>
+      <c r="C24">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>-1109</v>
+      </c>
+      <c r="C25">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>-1685</v>
+      </c>
+      <c r="C26">
+        <v>-645</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>-2021</v>
+      </c>
+      <c r="C27">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>-2069</v>
+      </c>
+      <c r="C28">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>-2133</v>
+      </c>
+      <c r="C29">
+        <v>-2197</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>-2133</v>
+      </c>
+      <c r="C30">
+        <v>-1557</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>-2149</v>
+      </c>
+      <c r="C31">
+        <v>-85</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>-2261</v>
+      </c>
+      <c r="C32">
+        <v>-1237</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1" xr:uid="{F2061EA4-28D3-4349-9580-4EA67BE3ACE4}"/>
+  <autoFilter ref="A1:C1" xr:uid="{F2061EA4-28D3-4349-9580-4EA67BE3ACE4}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C31">
+      <sortCondition descending="1" ref="B1:B31"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
